--- a/registration_forms/040_license_renewal_appointment_booking_form--registration_forms.xlsx
+++ b/registration_forms/040_license_renewal_appointment_booking_form--registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>select_license_type_other</t>
+          <t>select_license_type_other_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select Other License Type</t>
+          <t>Select License Type Other 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>select_license_status_other</t>
+          <t>select_license_status_other_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Select Other License Status</t>
+          <t>Select License Status Other 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>select_payment_method_other</t>
+          <t>select_payment_method_other_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Select Other Payment Method</t>
+          <t>Select Payment Method Other 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Select Other Payment Status</t>
+          <t>Payment Status Other</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Phone 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_license_type_other_choices</t>
+          <t>select_license_type_other_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_license_type_other_choices</t>
+          <t>select_license_type_other_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_license_status_other_choices</t>
+          <t>select_license_status_other_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_license_status_other_choices</t>
+          <t>select_license_status_other_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_payment_method_other_choices</t>
+          <t>select_payment_method_other_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1602,7 +1602,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_payment_method_other_choices</t>
+          <t>select_payment_method_other_2_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
